--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Lab Observation, ResourceType Observation</t>
+    <t>This StructureDefinition contains the maps for VistA ? (file ?) to FHIR Observation</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2579" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2579" uniqueCount="524">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -255,10 +255,10 @@
     <t>Mapping: SNOMED CT Attribute Binding</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -774,6 +774,10 @@
   </si>
   <si>
     <t>Coding.code</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-8:843: fixed value "laboratory" {null}</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -947,6 +951,9 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN
@@ -968,9 +975,6 @@
 SStaff.SMicroOrderedTest.LRDFN
 Micro.Virology.LRDFN
 Micro.VirologyReports.LRDFN</t>
-  </si>
-  <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Observation.focus</t>
@@ -2034,8 +2038,8 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="89.6171875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="89.6171875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4917,7 +4921,7 @@
         <v>84</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>106</v>
+        <v>244</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>84</v>
@@ -4926,10 +4930,10 @@
         <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>84</v>
@@ -4938,18 +4942,18 @@
         <v>84</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>84</v>
+        <v>247</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>246</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4975,14 +4979,14 @@
         <v>203</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5031,7 +5035,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5052,10 +5056,10 @@
         <v>84</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>84</v>
@@ -5072,10 +5076,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5098,19 +5102,19 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5159,7 +5163,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5180,10 +5184,10 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>84</v>
@@ -5200,10 +5204,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5229,16 +5233,16 @@
         <v>203</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5287,7 +5291,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5308,10 +5312,10 @@
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>84</v>
@@ -5328,13 +5332,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>190</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>84</v>
@@ -5378,7 +5382,7 @@
         <v>84</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>84</v>
@@ -5458,14 +5462,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5487,16 +5491,16 @@
         <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5521,13 +5525,13 @@
         <v>84</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>84</v>
@@ -5545,7 +5549,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>94</v>
@@ -5560,22 +5564,22 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5586,10 +5590,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5612,19 +5616,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5673,7 +5677,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5688,36 +5692,36 @@
         <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5740,16 +5744,16 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5799,7 +5803,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5820,13 +5824,13 @@
         <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>84</v>
@@ -5840,14 +5844,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5866,19 +5870,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -5927,7 +5931,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5942,19 +5946,19 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>84</v>
@@ -5968,14 +5972,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5994,19 +5998,19 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6055,7 +6059,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6064,25 +6068,25 @@
         <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>84</v>
@@ -6096,10 +6100,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6122,16 +6126,16 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6181,7 +6185,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6202,13 +6206,13 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>84</v>
@@ -6222,10 +6226,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6248,17 +6252,17 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6307,7 +6311,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6322,19 +6326,19 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>84</v>
@@ -6348,10 +6352,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6374,19 +6378,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6435,7 +6439,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6444,28 +6448,28 @@
         <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6476,10 +6480,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6505,16 +6509,16 @@
         <v>191</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6539,11 +6543,11 @@
         <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -6561,7 +6565,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6570,7 +6574,7 @@
         <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
@@ -6585,7 +6589,7 @@
         <v>137</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>84</v>
@@ -6602,14 +6606,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6631,16 +6635,16 @@
         <v>191</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6665,13 +6669,13 @@
         <v>84</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
@@ -6689,7 +6693,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6707,19 +6711,19 @@
         <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6730,10 +6734,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6756,19 +6760,19 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6817,7 +6821,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6838,10 +6842,10 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>84</v>
@@ -6858,10 +6862,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6887,13 +6891,13 @@
         <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6919,13 +6923,13 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -6943,7 +6947,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6961,19 +6965,19 @@
         <v>84</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -6984,10 +6988,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7013,16 +7017,16 @@
         <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7047,13 +7051,13 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
@@ -7071,7 +7075,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7092,10 +7096,10 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>84</v>
@@ -7112,10 +7116,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7138,16 +7142,16 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7197,7 +7201,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7215,19 +7219,19 @@
         <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7238,10 +7242,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7264,16 +7268,16 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7323,7 +7327,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7341,19 +7345,19 @@
         <v>84</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7364,10 +7368,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7390,19 +7394,19 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7451,7 +7455,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7463,7 +7467,7 @@
         <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>84</v>
@@ -7472,10 +7476,10 @@
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>84</v>
@@ -7492,10 +7496,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7616,10 +7620,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7742,14 +7746,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7771,10 +7775,10 @@
         <v>140</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>143</v>
@@ -7829,7 +7833,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7870,10 +7874,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7896,13 +7900,13 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7953,7 +7957,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7962,7 +7966,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7974,10 +7978,10 @@
         <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
@@ -7994,10 +7998,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8020,13 +8024,13 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8077,7 +8081,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8086,7 +8090,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -8098,10 +8102,10 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
@@ -8118,10 +8122,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8147,16 +8151,16 @@
         <v>191</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8184,10 +8188,10 @@
         <v>118</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8205,7 +8209,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8223,13 +8227,13 @@
         <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
@@ -8246,10 +8250,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8275,16 +8279,16 @@
         <v>191</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8309,13 +8313,13 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8333,7 +8337,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8351,13 +8355,13 @@
         <v>84</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
@@ -8374,10 +8378,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8400,17 +8404,17 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8459,7 +8463,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8483,7 +8487,7 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
@@ -8500,10 +8504,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8529,10 +8533,10 @@
         <v>203</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8583,7 +8587,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8604,10 +8608,10 @@
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
@@ -8624,10 +8628,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8650,16 +8654,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8709,7 +8713,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8730,10 +8734,10 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -8750,10 +8754,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8776,16 +8780,16 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8835,7 +8839,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8856,10 +8860,10 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>84</v>
@@ -8876,10 +8880,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8902,19 +8906,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -8963,7 +8967,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -8984,10 +8988,10 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
@@ -9004,10 +9008,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9128,10 +9132,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9254,14 +9258,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9283,10 +9287,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -9341,7 +9345,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9382,10 +9386,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9411,16 +9415,16 @@
         <v>191</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9445,13 +9449,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9469,7 +9473,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>94</v>
@@ -9487,16 +9491,16 @@
         <v>84</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>84</v>
@@ -9510,10 +9514,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9536,19 +9540,19 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9597,7 +9601,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9615,19 +9619,19 @@
         <v>84</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9638,10 +9642,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9667,16 +9671,16 @@
         <v>191</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -9701,13 +9705,13 @@
         <v>84</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>84</v>
@@ -9725,7 +9729,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9734,7 +9738,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9749,7 +9753,7 @@
         <v>137</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
@@ -9766,14 +9770,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9795,16 +9799,16 @@
         <v>191</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -9829,13 +9833,13 @@
         <v>84</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>84</v>
@@ -9853,7 +9857,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9871,19 +9875,19 @@
         <v>84</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -9894,10 +9898,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9923,16 +9927,16 @@
         <v>85</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -9981,7 +9985,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10002,10 +10006,10 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -777,7 +777,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-8:843: fixed value "laboratory" {null}</t>
+inv-9:843: fixed value = laboratory {null}</t>
   </si>
   <si>
     <t>C*E.1</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -777,7 +777,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-9:843: fixed value = laboratory {null}</t>
+inv-10:843: fixed value = laboratory {null}</t>
   </si>
   <si>
     <t>C*E.1</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA ? (file ?) to FHIR Observation</t>
+    <t>This StructureDefinition contains the maps for VistA file ? (#?) to us-core-observation-lab</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2579" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2579" uniqueCount="523">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Lab Observation {Observation}</t>
+    <t>Lab Observation Observation</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file ? (#?) to us-core-observation-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file PATIENT (#2) to us-core-observation-lab</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -774,10 +774,6 @@
   </si>
   <si>
     <t>Coding.code</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-10:843: fixed value = laboratory {null}</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -4841,7 +4837,7 @@
         <v>94</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>84</v>
@@ -4921,28 +4917,28 @@
         <v>84</v>
       </c>
       <c r="AJ23" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AK23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -4950,10 +4946,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4979,14 +4975,14 @@
         <v>203</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5035,7 +5031,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5056,10 +5052,10 @@
         <v>84</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>84</v>
@@ -5076,10 +5072,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5102,19 +5098,19 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5163,7 +5159,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5184,10 +5180,10 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>84</v>
@@ -5204,10 +5200,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5233,16 +5229,16 @@
         <v>203</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5291,7 +5287,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5312,10 +5308,10 @@
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>84</v>
@@ -5332,13 +5328,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>190</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>84</v>
@@ -5382,7 +5378,7 @@
         <v>84</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>84</v>
@@ -5462,14 +5458,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5491,16 +5487,16 @@
         <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5525,14 +5521,14 @@
         <v>84</v>
       </c>
       <c r="X28" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="Y28" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="Y28" t="s" s="2">
+      <c r="Z28" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>283</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>84</v>
       </c>
@@ -5549,7 +5545,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>94</v>
@@ -5564,22 +5560,22 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AO28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5590,10 +5586,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5616,19 +5612,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5677,7 +5673,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5692,36 +5688,36 @@
         <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AL29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AO29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ29" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AP29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
+      <c r="AR29" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AR29" t="s" s="2">
-        <v>301</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5744,16 +5740,16 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5803,7 +5799,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5824,13 +5820,13 @@
         <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>84</v>
@@ -5844,14 +5840,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5870,19 +5866,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -5931,7 +5927,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5946,19 +5942,19 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>84</v>
@@ -5972,14 +5968,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5998,19 +5994,19 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6059,7 +6055,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6068,25 +6064,25 @@
         <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AJ32" t="s" s="2">
+      <c r="AK32" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AK32" t="s" s="2">
+      <c r="AL32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>84</v>
@@ -6100,10 +6096,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6126,16 +6122,16 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6185,7 +6181,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6206,13 +6202,13 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>84</v>
@@ -6226,10 +6222,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6252,17 +6248,17 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6311,7 +6307,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6326,19 +6322,19 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>84</v>
@@ -6352,10 +6348,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6378,19 +6374,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6439,7 +6435,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6448,28 +6444,28 @@
         <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AJ35" t="s" s="2">
+      <c r="AK35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AK35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6480,10 +6476,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6509,16 +6505,16 @@
         <v>191</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6543,11 +6539,11 @@
         <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -6565,7 +6561,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6574,7 +6570,7 @@
         <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
@@ -6589,7 +6585,7 @@
         <v>137</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>84</v>
@@ -6606,14 +6602,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6635,16 +6631,16 @@
         <v>191</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6669,14 +6665,14 @@
         <v>84</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>376</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
       </c>
@@ -6693,7 +6689,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6711,19 +6707,19 @@
         <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6734,10 +6730,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6760,19 +6756,19 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6821,7 +6817,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6842,10 +6838,10 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>84</v>
@@ -6862,10 +6858,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6891,13 +6887,13 @@
         <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6923,14 +6919,14 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="Y39" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="Y39" t="s" s="2">
+      <c r="Z39" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>395</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
       </c>
@@ -6947,7 +6943,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6965,19 +6961,19 @@
         <v>84</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -6988,10 +6984,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7017,16 +7013,16 @@
         <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7051,14 +7047,14 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>406</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
       </c>
@@ -7075,7 +7071,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7096,10 +7092,10 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>84</v>
@@ -7116,10 +7112,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7142,16 +7138,16 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7201,7 +7197,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7219,19 +7215,19 @@
         <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7242,10 +7238,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7268,16 +7264,16 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7327,7 +7323,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7345,19 +7341,19 @@
         <v>84</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7368,10 +7364,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7394,19 +7390,19 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7455,7 +7451,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7467,19 +7463,19 @@
         <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AK43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>84</v>
@@ -7496,10 +7492,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7620,10 +7616,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7746,14 +7742,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7775,10 +7771,10 @@
         <v>140</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>143</v>
@@ -7833,7 +7829,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7874,10 +7870,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7900,13 +7896,13 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7957,7 +7953,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7966,7 +7962,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7978,10 +7974,10 @@
         <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
@@ -7998,10 +7994,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8024,13 +8020,13 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8081,7 +8077,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8090,7 +8086,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -8102,10 +8098,10 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
@@ -8122,10 +8118,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8151,16 +8147,16 @@
         <v>191</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8188,11 +8184,11 @@
         <v>118</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>460</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8209,7 +8205,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8227,13 +8223,13 @@
         <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>462</v>
-      </c>
       <c r="AN49" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
@@ -8250,10 +8246,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8279,16 +8275,16 @@
         <v>191</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8313,14 +8309,14 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>469</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
       </c>
@@ -8337,7 +8333,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8355,13 +8351,13 @@
         <v>84</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AM50" t="s" s="2">
-        <v>462</v>
-      </c>
       <c r="AN50" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
@@ -8378,10 +8374,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8404,17 +8400,17 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8463,7 +8459,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8487,7 +8483,7 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
@@ -8504,10 +8500,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8533,10 +8529,10 @@
         <v>203</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8587,7 +8583,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8608,10 +8604,10 @@
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
@@ -8628,10 +8624,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8654,16 +8650,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8713,7 +8709,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8734,10 +8730,10 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -8754,10 +8750,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8780,16 +8776,16 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8839,7 +8835,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8860,10 +8856,10 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>84</v>
@@ -8880,10 +8876,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8906,19 +8902,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -8967,7 +8963,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -8988,10 +8984,10 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
@@ -9008,10 +9004,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9132,10 +9128,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9258,14 +9254,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9287,10 +9283,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -9345,7 +9341,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9386,10 +9382,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9415,16 +9411,16 @@
         <v>191</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="N59" t="s" s="2">
-        <v>506</v>
-      </c>
       <c r="O59" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9449,13 +9445,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9473,7 +9469,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>94</v>
@@ -9491,16 +9487,16 @@
         <v>84</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>84</v>
@@ -9514,10 +9510,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9540,19 +9536,19 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="N60" t="s" s="2">
-        <v>512</v>
-      </c>
       <c r="O60" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9601,7 +9597,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9619,19 +9615,19 @@
         <v>84</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9642,10 +9638,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9671,16 +9667,16 @@
         <v>191</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="N61" t="s" s="2">
-        <v>517</v>
-      </c>
       <c r="O61" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -9705,13 +9701,13 @@
         <v>84</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>84</v>
@@ -9729,7 +9725,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9738,7 +9734,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9753,7 +9749,7 @@
         <v>137</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
@@ -9770,14 +9766,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9799,16 +9795,16 @@
         <v>191</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -9833,14 +9829,14 @@
         <v>84</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>376</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>84</v>
       </c>
@@ -9857,7 +9853,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9875,19 +9871,19 @@
         <v>84</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AN62" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -9898,10 +9894,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9927,16 +9923,16 @@
         <v>85</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>523</v>
-      </c>
       <c r="N63" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="O63" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -9985,7 +9981,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10006,10 +10002,10 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2579" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2579" uniqueCount="524">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -773,6 +773,9 @@
     <t>Need to refer to a particular code in the system.</t>
   </si>
   <si>
+    <t>laboratory</t>
+  </si>
+  <si>
     <t>Coding.code</t>
   </si>
   <si>
@@ -782,7 +785,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>843: fixed value = laboratory</t>
+    <t>843: fixed value = #laboratory</t>
   </si>
   <si>
     <t>Observation.category.coding.display</t>
@@ -4866,7 +4869,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>84</v>
+        <v>243</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -4905,7 +4908,7 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4926,10 +4929,10 @@
         <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>84</v>
@@ -4938,7 +4941,7 @@
         <v>84</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -4946,10 +4949,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4975,14 +4978,14 @@
         <v>203</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5031,7 +5034,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5052,10 +5055,10 @@
         <v>84</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>84</v>
@@ -5072,10 +5075,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5098,19 +5101,19 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5159,7 +5162,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5180,10 +5183,10 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>84</v>
@@ -5200,10 +5203,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5229,16 +5232,16 @@
         <v>203</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5287,7 +5290,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5308,10 +5311,10 @@
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>84</v>
@@ -5328,13 +5331,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>190</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>84</v>
@@ -5378,7 +5381,7 @@
         <v>84</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>84</v>
@@ -5458,14 +5461,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5487,16 +5490,16 @@
         <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5521,13 +5524,13 @@
         <v>84</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>84</v>
@@ -5545,7 +5548,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>94</v>
@@ -5560,22 +5563,22 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5586,10 +5589,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5612,19 +5615,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5673,7 +5676,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5688,36 +5691,36 @@
         <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5740,16 +5743,16 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5799,7 +5802,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5820,13 +5823,13 @@
         <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>84</v>
@@ -5840,14 +5843,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5866,19 +5869,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -5927,7 +5930,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5942,19 +5945,19 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>84</v>
@@ -5968,14 +5971,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5994,19 +5997,19 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6055,7 +6058,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6064,25 +6067,25 @@
         <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>84</v>
@@ -6096,10 +6099,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6122,16 +6125,16 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6181,7 +6184,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6202,13 +6205,13 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>84</v>
@@ -6222,10 +6225,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6248,17 +6251,17 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6307,7 +6310,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6322,19 +6325,19 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>84</v>
@@ -6348,10 +6351,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6374,19 +6377,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6435,7 +6438,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6444,28 +6447,28 @@
         <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6476,10 +6479,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6505,16 +6508,16 @@
         <v>191</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6539,11 +6542,11 @@
         <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -6561,7 +6564,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6570,7 +6573,7 @@
         <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
@@ -6585,7 +6588,7 @@
         <v>137</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>84</v>
@@ -6602,14 +6605,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6631,16 +6634,16 @@
         <v>191</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6665,13 +6668,13 @@
         <v>84</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
@@ -6689,7 +6692,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6707,19 +6710,19 @@
         <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6730,10 +6733,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6756,19 +6759,19 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6817,7 +6820,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6838,10 +6841,10 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>84</v>
@@ -6858,10 +6861,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6887,13 +6890,13 @@
         <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6919,13 +6922,13 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -6943,7 +6946,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6961,19 +6964,19 @@
         <v>84</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -6984,10 +6987,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7013,16 +7016,16 @@
         <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7047,13 +7050,13 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
@@ -7071,7 +7074,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7092,10 +7095,10 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>84</v>
@@ -7112,10 +7115,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7138,16 +7141,16 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7197,7 +7200,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7215,19 +7218,19 @@
         <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7238,10 +7241,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7264,16 +7267,16 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7323,7 +7326,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7341,19 +7344,19 @@
         <v>84</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7364,10 +7367,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7390,19 +7393,19 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7451,7 +7454,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7463,7 +7466,7 @@
         <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>84</v>
@@ -7472,10 +7475,10 @@
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>84</v>
@@ -7492,10 +7495,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7616,10 +7619,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7742,14 +7745,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7771,10 +7774,10 @@
         <v>140</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>143</v>
@@ -7829,7 +7832,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7870,10 +7873,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7896,13 +7899,13 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7953,7 +7956,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7962,7 +7965,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7974,10 +7977,10 @@
         <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
@@ -7994,10 +7997,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8020,13 +8023,13 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8077,7 +8080,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8086,7 +8089,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -8098,10 +8101,10 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
@@ -8118,10 +8121,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8147,16 +8150,16 @@
         <v>191</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8184,10 +8187,10 @@
         <v>118</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8205,7 +8208,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8223,13 +8226,13 @@
         <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
@@ -8246,10 +8249,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8275,16 +8278,16 @@
         <v>191</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8309,13 +8312,13 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8333,7 +8336,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8351,13 +8354,13 @@
         <v>84</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
@@ -8374,10 +8377,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8400,17 +8403,17 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8459,7 +8462,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8483,7 +8486,7 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
@@ -8500,10 +8503,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8529,10 +8532,10 @@
         <v>203</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8583,7 +8586,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8604,10 +8607,10 @@
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
@@ -8624,10 +8627,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8650,16 +8653,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8709,7 +8712,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8730,10 +8733,10 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -8750,10 +8753,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8776,16 +8779,16 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8835,7 +8838,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8856,10 +8859,10 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>84</v>
@@ -8876,10 +8879,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8902,19 +8905,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -8963,7 +8966,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -8984,10 +8987,10 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
@@ -9004,10 +9007,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9128,10 +9131,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9254,14 +9257,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9283,10 +9286,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -9341,7 +9344,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9382,10 +9385,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9411,16 +9414,16 @@
         <v>191</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9445,13 +9448,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9469,7 +9472,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>94</v>
@@ -9487,16 +9490,16 @@
         <v>84</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>84</v>
@@ -9510,10 +9513,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9536,19 +9539,19 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9597,7 +9600,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9615,19 +9618,19 @@
         <v>84</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9638,10 +9641,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9667,16 +9670,16 @@
         <v>191</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -9701,13 +9704,13 @@
         <v>84</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>84</v>
@@ -9725,7 +9728,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9734,7 +9737,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9749,7 +9752,7 @@
         <v>137</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
@@ -9766,14 +9769,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9795,16 +9798,16 @@
         <v>191</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -9829,13 +9832,13 @@
         <v>84</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>84</v>
@@ -9853,7 +9856,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9871,19 +9874,19 @@
         <v>84</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -9894,10 +9897,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9923,16 +9926,16 @@
         <v>85</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -9981,7 +9984,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10002,10 +10005,10 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$52</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2579" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="462">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -626,245 +626,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Observation.category.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Observation.category.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>laboratory</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>843: fixed value = #laboratory</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Observation.category.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Observation.category:Laboratory</t>
-  </si>
-  <si>
-    <t>Laboratory</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -873,6 +634,34 @@
     &lt;code value="laboratory"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>843: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#laboratory</t>
+  </si>
+  <si>
+    <t>Observation.category:Laboratory</t>
+  </si>
+  <si>
+    <t>Laboratory</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -1402,7 +1191,29 @@
     <t>Observation.referenceRange.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Observation.referenceRange.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
   </si>
   <si>
     <t>Observation.referenceRange.modifierExtension</t>
@@ -1993,7 +1804,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR63"/>
+  <dimension ref="A1:AR52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -2024,7 +1835,7 @@
     <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
@@ -3863,7 +3674,7 @@
         <v>84</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>84</v>
+        <v>196</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>84</v>
@@ -3881,23 +3692,23 @@
         <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>190</v>
@@ -3924,16 +3735,16 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>84</v>
+        <v>203</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>84</v>
@@ -3941,24 +3752,26 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="D16" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>84</v>
@@ -3967,16 +3780,20 @@
         <v>84</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>84</v>
       </c>
@@ -3985,7 +3802,7 @@
         <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>84</v>
+        <v>196</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>84</v>
@@ -4000,13 +3817,13 @@
         <v>84</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>84</v>
+        <v>197</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>84</v>
@@ -4024,19 +3841,19 @@
         <v>84</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>84</v>
@@ -4048,10 +3865,10 @@
         <v>84</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>84</v>
@@ -4065,44 +3882,46 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>139</v>
+        <v>207</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>140</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
         <v>209</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>84</v>
       </c>
@@ -4126,61 +3945,61 @@
         <v>84</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>84</v>
+        <v>212</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>84</v>
+        <v>213</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>211</v>
+        <v>84</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>84</v>
+        <v>216</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>84</v>
+        <v>217</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>84</v>
+        <v>219</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>84</v>
+        <v>220</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>84</v>
@@ -4191,10 +4010,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4202,13 +4021,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>84</v>
@@ -4217,19 +4036,19 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>84</v>
@@ -4278,13 +4097,13 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>84</v>
@@ -4293,36 +4112,36 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>84</v>
+        <v>227</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AR18" t="s" s="2">
-        <v>84</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4333,7 +4152,7 @@
         <v>82</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>84</v>
@@ -4342,18 +4161,20 @@
         <v>84</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>84</v>
@@ -4402,19 +4223,19 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>84</v>
@@ -4423,13 +4244,13 @@
         <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>84</v>
+        <v>217</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>84</v>
@@ -4443,21 +4264,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>139</v>
+        <v>240</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>84</v>
@@ -4466,21 +4287,23 @@
         <v>84</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>140</v>
+        <v>241</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>141</v>
+        <v>242</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
       </c>
@@ -4516,46 +4339,46 @@
         <v>84</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>211</v>
+        <v>84</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>84</v>
+        <v>246</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>84</v>
+        <v>247</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>207</v>
+        <v>248</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>84</v>
+        <v>249</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>84</v>
@@ -4569,14 +4392,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>84</v>
+        <v>251</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4586,7 +4409,7 @@
         <v>94</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>84</v>
@@ -4595,19 +4418,19 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>108</v>
+        <v>252</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -4656,7 +4479,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4665,25 +4488,25 @@
         <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>84</v>
+        <v>257</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>106</v>
+        <v>258</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>84</v>
+        <v>259</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>84</v>
+        <v>262</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>84</v>
@@ -4697,10 +4520,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4723,16 +4546,16 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>203</v>
+        <v>264</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4782,7 +4605,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4803,13 +4626,13 @@
         <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>84</v>
+        <v>270</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>84</v>
@@ -4823,10 +4646,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>271</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>271</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4837,10 +4660,10 @@
         <v>82</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>84</v>
@@ -4849,17 +4672,17 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>114</v>
+        <v>272</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>273</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
+        <v>274</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>242</v>
+        <v>275</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -4869,7 +4692,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>243</v>
+        <v>84</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -4908,13 +4731,13 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>84</v>
@@ -4923,25 +4746,25 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>84</v>
+        <v>276</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>84</v>
+        <v>279</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>247</v>
+        <v>84</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -4949,10 +4772,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4966,7 +4789,7 @@
         <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>84</v>
@@ -4975,17 +4798,19 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>203</v>
+        <v>281</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>249</v>
+        <v>282</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O24" t="s" s="2">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5034,7 +4859,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5043,28 +4868,28 @@
         <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>84</v>
+        <v>286</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>84</v>
+        <v>288</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>254</v>
+        <v>290</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>84</v>
+        <v>291</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>84</v>
@@ -5075,10 +4900,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5092,28 +4917,28 @@
         <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>256</v>
+        <v>191</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>257</v>
+        <v>293</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5138,13 +4963,11 @@
         <v>84</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>84</v>
+        <v>297</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
@@ -5162,7 +4985,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5171,7 +4994,7 @@
         <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>84</v>
+        <v>298</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>106</v>
@@ -5183,10 +5006,10 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>262</v>
+        <v>137</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>263</v>
+        <v>299</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>84</v>
@@ -5203,21 +5026,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>84</v>
+        <v>301</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>84</v>
@@ -5226,22 +5049,22 @@
         <v>84</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>265</v>
+        <v>302</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>268</v>
+        <v>305</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5266,13 +5089,13 @@
         <v>84</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>84</v>
+        <v>212</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>84</v>
+        <v>306</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>84</v>
+        <v>307</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>84</v>
@@ -5290,13 +5113,13 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>84</v>
@@ -5308,19 +5131,19 @@
         <v>84</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>84</v>
+        <v>308</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>271</v>
+        <v>310</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>84</v>
+        <v>311</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
@@ -5331,26 +5154,24 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>272</v>
+        <v>312</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>84</v>
@@ -5359,19 +5180,19 @@
         <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>191</v>
+        <v>313</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>192</v>
+        <v>314</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>193</v>
+        <v>315</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>194</v>
+        <v>316</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>195</v>
+        <v>317</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5381,7 +5202,7 @@
         <v>84</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>274</v>
+        <v>84</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>84</v>
@@ -5396,13 +5217,13 @@
         <v>84</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>196</v>
+        <v>84</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>197</v>
+        <v>84</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>84</v>
@@ -5420,7 +5241,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>190</v>
+        <v>312</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5441,13 +5262,13 @@
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>84</v>
+        <v>318</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>200</v>
+        <v>319</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>84</v>
@@ -5461,46 +5282,44 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>276</v>
+        <v>84</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>277</v>
+        <v>321</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>278</v>
+        <v>322</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>84</v>
       </c>
@@ -5524,13 +5343,13 @@
         <v>84</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>281</v>
+        <v>324</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>282</v>
+        <v>325</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>283</v>
+        <v>326</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>84</v>
@@ -5548,10 +5367,10 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>94</v>
@@ -5563,22 +5382,22 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>284</v>
+        <v>84</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>285</v>
+        <v>327</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>286</v>
+        <v>328</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>287</v>
+        <v>329</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>288</v>
+        <v>84</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>289</v>
+        <v>330</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5589,10 +5408,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>290</v>
+        <v>331</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>290</v>
+        <v>331</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5600,34 +5419,34 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>291</v>
+        <v>191</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>292</v>
+        <v>332</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>293</v>
+        <v>333</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>294</v>
+        <v>334</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>295</v>
+        <v>335</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5652,13 +5471,13 @@
         <v>84</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>84</v>
+        <v>324</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>84</v>
+        <v>336</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>84</v>
+        <v>337</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>84</v>
@@ -5676,7 +5495,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>290</v>
+        <v>331</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5691,36 +5510,36 @@
         <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>296</v>
+        <v>84</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>297</v>
+        <v>338</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>298</v>
+        <v>339</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>299</v>
+        <v>84</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>300</v>
+        <v>84</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>301</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>340</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>340</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5731,7 +5550,7 @@
         <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>84</v>
@@ -5740,19 +5559,19 @@
         <v>84</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>303</v>
+        <v>341</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>304</v>
+        <v>342</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>305</v>
+        <v>343</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>306</v>
+        <v>344</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5802,13 +5621,13 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>302</v>
+        <v>340</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>84</v>
@@ -5820,19 +5639,19 @@
         <v>84</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>84</v>
+        <v>345</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>286</v>
+        <v>346</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>307</v>
+        <v>347</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>299</v>
+        <v>84</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>84</v>
+        <v>348</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>84</v>
@@ -5843,14 +5662,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>309</v>
+        <v>84</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5866,23 +5685,21 @@
         <v>84</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>311</v>
+        <v>351</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>312</v>
+        <v>352</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>84</v>
       </c>
@@ -5930,7 +5747,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5945,22 +5762,22 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>315</v>
+        <v>84</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>84</v>
+        <v>354</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>316</v>
+        <v>355</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>317</v>
+        <v>356</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>318</v>
+        <v>84</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>84</v>
+        <v>357</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -5971,45 +5788,45 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>320</v>
+        <v>84</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>321</v>
+        <v>359</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>322</v>
+        <v>360</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>323</v>
+        <v>361</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>325</v>
+        <v>363</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6058,34 +5875,34 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>326</v>
+        <v>84</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>327</v>
+        <v>364</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>328</v>
+        <v>84</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>329</v>
+        <v>365</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>331</v>
+        <v>84</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>84</v>
@@ -6099,10 +5916,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>332</v>
+        <v>367</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>332</v>
+        <v>367</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6122,20 +5939,18 @@
         <v>84</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>333</v>
+        <v>368</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>334</v>
+        <v>369</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6184,7 +5999,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>332</v>
+        <v>371</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6196,7 +6011,7 @@
         <v>84</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>84</v>
@@ -6205,13 +6020,13 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>337</v>
+        <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>338</v>
+        <v>372</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>339</v>
+        <v>84</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>84</v>
@@ -6225,14 +6040,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>340</v>
+        <v>373</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>340</v>
+        <v>373</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6248,21 +6063,21 @@
         <v>84</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>341</v>
+        <v>140</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>342</v>
+        <v>141</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>84</v>
       </c>
@@ -6310,7 +6125,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>340</v>
+        <v>375</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6322,22 +6137,22 @@
         <v>84</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>345</v>
+        <v>84</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>346</v>
+        <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>348</v>
+        <v>84</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>84</v>
@@ -6351,45 +6166,45 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>349</v>
+        <v>376</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>349</v>
+        <v>376</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>84</v>
+        <v>377</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I35" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>350</v>
+        <v>140</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>353</v>
+        <v>143</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>354</v>
+        <v>149</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6438,37 +6253,37 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>349</v>
+        <v>380</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>355</v>
+        <v>84</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>356</v>
+        <v>145</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>357</v>
+        <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>358</v>
+        <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>359</v>
+        <v>137</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>360</v>
+        <v>84</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6479,10 +6294,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6496,7 +6311,7 @@
         <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
@@ -6505,20 +6320,16 @@
         <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>191</v>
+        <v>382</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>84</v>
       </c>
@@ -6542,11 +6353,13 @@
         <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z36" t="s" s="2">
-        <v>366</v>
+        <v>84</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -6564,7 +6377,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6573,7 +6386,7 @@
         <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
@@ -6585,10 +6398,10 @@
         <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>137</v>
+        <v>386</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>84</v>
@@ -6605,21 +6418,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>370</v>
+        <v>84</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>84</v>
@@ -6631,20 +6444,16 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>191</v>
+        <v>382</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>84</v>
       </c>
@@ -6668,13 +6477,13 @@
         <v>84</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>281</v>
+        <v>84</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>375</v>
+        <v>84</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>376</v>
+        <v>84</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
@@ -6692,16 +6501,16 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>84</v>
+        <v>385</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
@@ -6710,19 +6519,19 @@
         <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>377</v>
+        <v>84</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>380</v>
+        <v>84</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6733,10 +6542,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6747,7 +6556,7 @@
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>84</v>
@@ -6759,19 +6568,19 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>382</v>
+        <v>191</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6796,13 +6605,13 @@
         <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>84</v>
+        <v>397</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>84</v>
+        <v>398</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6820,13 +6629,13 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>84</v>
@@ -6838,13 +6647,13 @@
         <v>84</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>84</v>
+        <v>399</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>388</v>
+        <v>310</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>84</v>
@@ -6861,10 +6670,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6875,7 +6684,7 @@
         <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>84</v>
@@ -6890,15 +6699,17 @@
         <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
       </c>
@@ -6922,13 +6733,13 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>393</v>
+        <v>324</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -6946,13 +6757,13 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>84</v>
@@ -6964,19 +6775,19 @@
         <v>84</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>398</v>
+        <v>310</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>399</v>
+        <v>84</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -6987,10 +6798,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7013,19 +6824,17 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>191</v>
+        <v>409</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7050,13 +6859,13 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>393</v>
+        <v>84</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>405</v>
+        <v>84</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>406</v>
+        <v>84</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
@@ -7074,7 +6883,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7095,10 +6904,10 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>407</v>
+        <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>84</v>
@@ -7115,10 +6924,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7141,17 +6950,15 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>410</v>
+        <v>368</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7200,7 +7007,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7218,19 +7025,19 @@
         <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>414</v>
+        <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>415</v>
+        <v>386</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>417</v>
+        <v>84</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7255,7 +7062,7 @@
         <v>82</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>84</v>
@@ -7264,7 +7071,7 @@
         <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>419</v>
@@ -7332,7 +7139,7 @@
         <v>82</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>84</v>
@@ -7344,19 +7151,19 @@
         <v>84</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AN42" t="s" s="2">
-        <v>425</v>
-      </c>
       <c r="AO42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>426</v>
+        <v>84</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7367,10 +7174,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7390,23 +7197,21 @@
         <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>432</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>84</v>
       </c>
@@ -7454,7 +7259,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7466,7 +7271,7 @@
         <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>433</v>
+        <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>84</v>
@@ -7475,10 +7280,10 @@
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>84</v>
@@ -7495,10 +7300,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7509,7 +7314,7 @@
         <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>84</v>
@@ -7518,19 +7323,23 @@
         <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>203</v>
+        <v>359</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>204</v>
+        <v>432</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
       </c>
@@ -7578,19 +7387,19 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>206</v>
+        <v>431</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
@@ -7599,10 +7408,10 @@
         <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>84</v>
+        <v>436</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>207</v>
+        <v>437</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
@@ -7619,21 +7428,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>84</v>
@@ -7645,17 +7454,15 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>140</v>
+        <v>368</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>141</v>
+        <v>369</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7704,19 +7511,19 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>212</v>
+        <v>371</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
@@ -7728,7 +7535,7 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>207</v>
+        <v>372</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
@@ -7745,14 +7552,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>439</v>
+        <v>139</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7765,26 +7572,24 @@
         <v>84</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>440</v>
+        <v>141</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>441</v>
+        <v>374</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O46" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>84</v>
       </c>
@@ -7832,7 +7637,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>442</v>
+        <v>375</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7856,7 +7661,7 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>137</v>
+        <v>372</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -7873,42 +7678,46 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>84</v>
+        <v>377</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>444</v>
+        <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>445</v>
+        <v>378</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
       </c>
@@ -7956,19 +7765,19 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>443</v>
+        <v>380</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>447</v>
+        <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>84</v>
@@ -7977,10 +7786,10 @@
         <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>448</v>
+        <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>449</v>
+        <v>137</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
@@ -7997,10 +7806,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8008,7 +7817,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>94</v>
@@ -8020,19 +7829,23 @@
         <v>84</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L48" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8056,13 +7869,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>84</v>
+        <v>324</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>84</v>
+        <v>445</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8080,16 +7893,16 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>447</v>
+        <v>84</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -8098,16 +7911,16 @@
         <v>84</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>84</v>
+        <v>446</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>448</v>
+        <v>217</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>453</v>
+        <v>218</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>84</v>
+        <v>219</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>84</v>
@@ -8121,10 +7934,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8144,22 +7957,22 @@
         <v>84</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>191</v>
+        <v>281</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>458</v>
+        <v>285</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8184,13 +7997,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>459</v>
+        <v>84</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>460</v>
+        <v>84</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8208,7 +8021,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8226,19 +8039,19 @@
         <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>462</v>
+        <v>289</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>379</v>
+        <v>290</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>84</v>
+        <v>291</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8249,10 +8062,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8263,7 +8076,7 @@
         <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>84</v>
@@ -8278,16 +8091,16 @@
         <v>191</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>467</v>
+        <v>296</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8312,13 +8125,13 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>393</v>
+        <v>212</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>469</v>
+        <v>297</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8336,16 +8149,16 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>84</v>
+        <v>457</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
@@ -8354,13 +8167,13 @@
         <v>84</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>461</v>
+        <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>462</v>
+        <v>137</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>379</v>
+        <v>299</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
@@ -8377,21 +8190,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>84</v>
+        <v>301</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>84</v>
@@ -8403,17 +8216,19 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>471</v>
+        <v>191</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>472</v>
+        <v>302</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="O51" t="s" s="2">
-        <v>474</v>
+        <v>305</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8438,13 +8253,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>84</v>
+        <v>212</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>84</v>
+        <v>306</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>84</v>
+        <v>307</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8462,13 +8277,13 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>84</v>
@@ -8480,19 +8295,19 @@
         <v>84</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>84</v>
+        <v>308</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>84</v>
+        <v>309</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>475</v>
+        <v>310</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>84</v>
+        <v>311</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8503,10 +8318,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8517,7 +8332,7 @@
         <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>84</v>
@@ -8529,16 +8344,20 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>203</v>
+        <v>85</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>477</v>
+        <v>460</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
       </c>
@@ -8586,13 +8405,13 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>84</v>
@@ -8607,10 +8426,10 @@
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>448</v>
+        <v>365</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>479</v>
+        <v>366</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
@@ -8622,1409 +8441,11 @@
         <v>84</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR53" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="54" hidden="true">
-      <c r="A54" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR54" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="P55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR55" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR56" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O57" s="2"/>
-      <c r="P57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR57" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="P58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR58" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR59" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="P60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR60" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="P61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR61" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="P62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR62" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR63" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR63">
+  <autoFilter ref="A1:AR52">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10034,7 +8455,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI62">
+  <conditionalFormatting sqref="A2:AI51">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,7 +713,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,7 +713,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$52</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2189" uniqueCount="464">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
+    <t>Mapping: Virtual Patient Record (VPR)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -733,6 +736,27 @@
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.LRDFN
+Micro.AntibioticSensitivityComment.LRDFN
+Micro.BacteriologyReports.LRDFN
+Micro.MicroAntibioticLevel.LRDFN
+Micro.MicroAudit.LRDFN
+Micro.Microbiology.LRDFN
+Micro.MicroOrderedTest.LRDFN
+Micro.MicroSterilityResults.LRDFN
+Micro.MycobacteriologyReports.LRDFN
+Micro.Mycology.LRDFN
+Micro.MycologyReports.LRDFN
+Micro.Parasitology.LRDFN
+Micro.ParasitologyReports.LRDFN
+Micro.ParasitologyStage.LRDFN
+Micro.Virology.LRDFN
+Micro.VirologyReports.LRDFN
+Pathology.Autopsy.LRDFN
+Pathology.CytoOrganTissueFunction.StaffIEN
+SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1786,7 +1810,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR52"/>
+  <dimension ref="A1:AS52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -1826,12 +1850,13 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="42.265625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1967,6 +1992,9 @@
       <c r="AR1" t="s" s="1">
         <v>80</v>
       </c>
+      <c r="AS1" t="s" s="1">
+        <v>81</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1977,106 +2005,106 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>90</v>
@@ -2088,1135 +2116,1162 @@
         <v>92</v>
       </c>
       <c r="AQ2" t="s" s="2">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="AR2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS2" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AQ3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AR3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS3" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AQ4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AR4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS4" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AQ5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AR5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS5" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AQ6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AR6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS6" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP7" t="s" s="2">
-        <v>129</v>
+        <v>85</v>
       </c>
       <c r="AQ7" t="s" s="2">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="AR7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS7" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH8" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP8" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ8" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS8" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH9" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AG9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP9" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ9" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS9" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH10" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AG10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP10" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ10" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS10" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH11" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>85</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>157</v>
+        <v>85</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>158</v>
@@ -3225,370 +3280,379 @@
         <v>159</v>
       </c>
       <c r="AR11" t="s" s="2">
-        <v>84</v>
+        <v>160</v>
+      </c>
+      <c r="AS11" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH12" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>167</v>
+        <v>85</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>168</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AR12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS12" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH13" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>177</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>84</v>
+        <v>178</v>
       </c>
       <c r="AR13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS13" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>185</v>
+        <v>85</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>186</v>
@@ -3603,376 +3667,385 @@
         <v>189</v>
       </c>
       <c r="AR14" t="s" s="2">
-        <v>84</v>
+        <v>190</v>
+      </c>
+      <c r="AS14" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH15" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AE15" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>202</v>
+        <v>85</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>203</v>
       </c>
       <c r="AR15" t="s" s="2">
-        <v>84</v>
+        <v>204</v>
+      </c>
+      <c r="AS15" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH16" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S16" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>202</v>
+        <v>85</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>203</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>84</v>
+        <v>204</v>
+      </c>
+      <c r="AS16" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>215</v>
+        <v>85</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>216</v>
@@ -3988,3921 +4061,4014 @@
       </c>
       <c r="AR17" t="s" s="2">
         <v>220</v>
+      </c>
+      <c r="AS17" t="s" s="2">
+        <v>221</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AR18" t="s" s="2">
-        <v>84</v>
+        <v>234</v>
+      </c>
+      <c r="AS18" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH19" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>217</v>
+        <v>85</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>84</v>
+        <v>234</v>
+      </c>
+      <c r="AS19" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>246</v>
+        <v>85</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>84</v>
+        <v>248</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>247</v>
+        <v>85</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>84</v>
+        <v>251</v>
+      </c>
+      <c r="AS20" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>259</v>
+        <v>85</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>84</v>
+        <v>261</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>260</v>
+        <v>85</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>84</v>
+        <v>264</v>
+      </c>
+      <c r="AS21" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>268</v>
+        <v>85</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>84</v>
+        <v>272</v>
+      </c>
+      <c r="AS22" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH23" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>276</v>
+        <v>85</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>277</v>
+        <v>85</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>84</v>
+        <v>281</v>
+      </c>
+      <c r="AS23" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>288</v>
+        <v>85</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>291</v>
+        <v>85</v>
+      </c>
+      <c r="AS24" t="s" s="2">
+        <v>293</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>299</v>
+        <v>138</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>84</v>
+        <v>301</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS25" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH26" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>308</v>
+        <v>85</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>311</v>
+        <v>85</v>
+      </c>
+      <c r="AS26" t="s" s="2">
+        <v>313</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH27" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>318</v>
+        <v>85</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>84</v>
+        <v>321</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS27" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>327</v>
+        <v>85</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>84</v>
+        <v>331</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>330</v>
+        <v>85</v>
+      </c>
+      <c r="AS28" t="s" s="2">
+        <v>332</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="P29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>338</v>
+        <v>85</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>84</v>
+        <v>341</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS29" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>345</v>
+        <v>85</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>84</v>
+        <v>349</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>348</v>
+        <v>85</v>
+      </c>
+      <c r="AS30" t="s" s="2">
+        <v>350</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>354</v>
+        <v>85</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>84</v>
+        <v>358</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>357</v>
+        <v>85</v>
+      </c>
+      <c r="AS31" t="s" s="2">
+        <v>359</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH32" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>365</v>
+        <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>84</v>
+        <v>368</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS32" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>372</v>
+        <v>85</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>84</v>
+        <v>374</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS33" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH34" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>372</v>
+        <v>85</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>84</v>
+        <v>374</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS34" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH35" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS35" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>386</v>
+        <v>85</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>84</v>
+        <v>389</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS36" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AG37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AQ37" t="s" s="2">
-        <v>84</v>
+        <v>393</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS37" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AA38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>399</v>
+        <v>85</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>310</v>
+        <v>402</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS38" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH39" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF39" t="s" s="2">
+      <c r="AI39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AG39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>400</v>
-      </c>
       <c r="AP39" t="s" s="2">
-        <v>310</v>
+        <v>402</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS39" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="P40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>413</v>
+        <v>85</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>84</v>
+        <v>415</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS40" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>386</v>
+        <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>417</v>
+        <v>388</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>84</v>
+        <v>419</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS41" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH42" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>423</v>
+        <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>84</v>
+        <v>426</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS42" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH43" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF43" t="s" s="2">
+      <c r="AI43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AG43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>430</v>
-      </c>
       <c r="AQ43" t="s" s="2">
-        <v>84</v>
+        <v>432</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS43" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="P44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH44" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>436</v>
+        <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>84</v>
+        <v>439</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS44" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>372</v>
+        <v>85</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>84</v>
+        <v>374</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS45" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH46" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>372</v>
+        <v>85</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>84</v>
+        <v>374</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS46" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH47" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS47" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AA48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>446</v>
+        <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>217</v>
+        <v>448</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>218</v>
@@ -7911,523 +8077,538 @@
         <v>219</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>84</v>
+        <v>220</v>
+      </c>
+      <c r="AS48" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>451</v>
+        <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>289</v>
+        <v>453</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>291</v>
+        <v>85</v>
+      </c>
+      <c r="AS49" t="s" s="2">
+        <v>293</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AA50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>299</v>
+        <v>138</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>84</v>
+        <v>301</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS50" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH51" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>308</v>
+        <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>311</v>
+        <v>85</v>
+      </c>
+      <c r="AS51" t="s" s="2">
+        <v>313</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH52" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>365</v>
+        <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>84</v>
+        <v>368</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS52" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR52">
+  <autoFilter ref="A1:AS52">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$52</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2189" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="462">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -241,9 +241,6 @@
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -716,7 +713,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -736,27 +733,6 @@
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
-  </si>
-  <si>
-    <t>Micro.AntibioticSensitivity.LRDFN
-Micro.AntibioticSensitivityComment.LRDFN
-Micro.BacteriologyReports.LRDFN
-Micro.MicroAntibioticLevel.LRDFN
-Micro.MicroAudit.LRDFN
-Micro.Microbiology.LRDFN
-Micro.MicroOrderedTest.LRDFN
-Micro.MicroSterilityResults.LRDFN
-Micro.MycobacteriologyReports.LRDFN
-Micro.Mycology.LRDFN
-Micro.MycologyReports.LRDFN
-Micro.Parasitology.LRDFN
-Micro.ParasitologyReports.LRDFN
-Micro.ParasitologyStage.LRDFN
-Micro.Virology.LRDFN
-Micro.VirologyReports.LRDFN
-Pathology.Autopsy.LRDFN
-Pathology.CytoOrganTissueFunction.StaffIEN
-SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1810,7 +1786,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS52"/>
+  <dimension ref="A1:AR52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -1850,13 +1826,12 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="42.265625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1992,9 +1967,6 @@
       <c r="AR1" t="s" s="1">
         <v>80</v>
       </c>
-      <c r="AS1" t="s" s="1">
-        <v>81</v>
-      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -2005,106 +1977,106 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G2" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G2" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I2" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K2" t="s" s="2">
+      <c r="L2" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L2" t="s" s="2">
+      <c r="M2" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="M2" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="N2" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH2" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH2" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AK2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AK2" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL2" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>90</v>
@@ -2116,1162 +2088,1135 @@
         <v>92</v>
       </c>
       <c r="AQ2" t="s" s="2">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="AR2" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS2" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>100</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AQ3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AR3" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AG4" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>107</v>
-      </c>
       <c r="AK4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AQ4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AR4" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AQ5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AR5" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>122</v>
-      </c>
       <c r="AG6" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AQ6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AR6" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="AG7" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="AQ7" t="s" s="2">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="AR7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G8" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G8" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AG8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="AQ8" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="AR8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G9" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G9" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF9" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="AG9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI9" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ9" t="s" s="2">
-        <v>146</v>
-      </c>
       <c r="AK9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP9" t="s" s="2">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="AQ9" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="AR9" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G10" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G10" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N10" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>150</v>
-      </c>
       <c r="P10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH10" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH10" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP10" t="s" s="2">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="AQ10" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="AR10" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G11" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G11" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH11" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH11" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>85</v>
+        <v>156</v>
       </c>
       <c r="AN11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>158</v>
@@ -3280,379 +3225,370 @@
         <v>159</v>
       </c>
       <c r="AR11" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AS11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G12" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G12" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH12" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH12" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="AN12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>168</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AR12" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G13" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G13" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH13" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH13" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="AN13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO13" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>177</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>178</v>
+        <v>84</v>
       </c>
       <c r="AR13" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H14" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="G14" t="s" s="2">
+      <c r="I14" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H14" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="J14" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="O14" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="P14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>186</v>
@@ -3667,385 +3603,376 @@
         <v>189</v>
       </c>
       <c r="AR14" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AS14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H15" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="G15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="I15" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="O15" t="s" s="2">
-        <v>196</v>
-      </c>
       <c r="P15" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S15" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="T15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X15" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE15" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK15" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AF15" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK15" t="s" s="2">
+      <c r="AL15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>203</v>
       </c>
       <c r="AR15" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AS15" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="C16" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="B16" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="D16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H16" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="I16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="O16" t="s" s="2">
-        <v>196</v>
-      </c>
       <c r="P16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="T16" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>199</v>
-      </c>
       <c r="AA16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH16" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH16" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>85</v>
+        <v>202</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>203</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AS16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H17" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="G17" t="s" s="2">
+      <c r="I17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J17" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H17" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="K17" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="O17" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="P17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="Y17" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>216</v>
@@ -4061,4014 +3988,3921 @@
       </c>
       <c r="AR17" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AS17" t="s" s="2">
-        <v>221</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H18" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="G18" t="s" s="2">
+      <c r="I18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J18" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H18" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="K18" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="O18" t="s" s="2">
-        <v>227</v>
-      </c>
       <c r="P18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AO18" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP18" t="s" s="2">
+      <c r="AQ18" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AQ18" t="s" s="2">
-        <v>233</v>
-      </c>
       <c r="AR18" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AS18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G19" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G19" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH19" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH19" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>85</v>
+        <v>217</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AS19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="K20" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N20" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>247</v>
-      </c>
       <c r="P20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>85</v>
+        <v>246</v>
       </c>
       <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AP20" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AO20" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP20" t="s" s="2">
+      <c r="AQ20" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AQ20" t="s" s="2">
-        <v>250</v>
-      </c>
       <c r="AR20" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AS20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G21" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H21" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H21" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="I21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="N21" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>258</v>
-      </c>
       <c r="P21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AJ21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AK21" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AO21" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP21" t="s" s="2">
+      <c r="AQ21" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AQ21" t="s" s="2">
-        <v>263</v>
-      </c>
       <c r="AR21" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AS21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G22" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H22" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="K22" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>85</v>
+        <v>268</v>
       </c>
       <c r="AP22" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AQ22" t="s" s="2">
-        <v>271</v>
-      </c>
       <c r="AR22" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AS22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G23" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G23" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="P23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AG23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH23" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH23" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>85</v>
+        <v>276</v>
       </c>
       <c r="AN23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AO23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AQ23" t="s" s="2">
-        <v>280</v>
-      </c>
       <c r="AR23" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AS23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H24" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="I24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N24" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>287</v>
-      </c>
       <c r="P24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AJ24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AK24" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AP24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR24" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AR24" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS24" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G25" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H25" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="I25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="N25" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="P25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP25" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AA25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>138</v>
-      </c>
       <c r="AQ25" t="s" s="2">
-        <v>301</v>
+        <v>84</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS25" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G26" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G26" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="N26" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>307</v>
-      </c>
       <c r="P26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="Z26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AA26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AP26" t="s" s="2">
+      <c r="AQ26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR26" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AR26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS26" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G27" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G27" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="N27" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>319</v>
-      </c>
       <c r="P27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH27" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH27" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>85</v>
+        <v>318</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>321</v>
+        <v>84</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS27" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X28" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Y28" t="s" s="2">
+      <c r="AA28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="Z28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AA28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AP28" t="s" s="2">
+      <c r="AQ28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR28" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS28" t="s" s="2">
-        <v>332</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="N29" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>337</v>
-      </c>
       <c r="P29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="Z29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AA29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>340</v>
-      </c>
       <c r="AQ29" t="s" s="2">
-        <v>341</v>
+        <v>84</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>85</v>
+        <v>345</v>
       </c>
       <c r="AO30" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AP30" t="s" s="2">
+      <c r="AQ30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR30" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AR30" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS30" t="s" s="2">
-        <v>350</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>85</v>
+        <v>354</v>
       </c>
       <c r="AO31" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AP31" t="s" s="2">
+      <c r="AQ31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR31" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AR31" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS31" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G32" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G32" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N32" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>365</v>
-      </c>
       <c r="P32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AG32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH32" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH32" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AK32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>367</v>
-      </c>
       <c r="AQ32" t="s" s="2">
-        <v>368</v>
+        <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>85</v>
+        <v>372</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G34" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G34" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="L34" t="s" s="2">
-        <v>142</v>
-      </c>
       <c r="M34" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AG34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH34" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH34" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>85</v>
+        <v>372</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G35" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G35" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH35" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH35" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO36" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AP36" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>388</v>
-      </c>
       <c r="AQ36" t="s" s="2">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS36" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>85</v>
+        <v>386</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>393</v>
+        <v>84</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="N38" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="P38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="Z38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AA38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>401</v>
-      </c>
       <c r="AP38" t="s" s="2">
-        <v>402</v>
+        <v>310</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>312</v>
+        <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G39" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G39" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="N39" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="P39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AG39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH39" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH39" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>85</v>
+        <v>399</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>402</v>
+        <v>310</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>312</v>
+        <v>84</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>85</v>
+        <v>413</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>415</v>
+        <v>84</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>85</v>
+        <v>386</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>419</v>
+        <v>84</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G42" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G42" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AG42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH42" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH42" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>85</v>
+        <v>423</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>426</v>
+        <v>84</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G43" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G43" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AG43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH43" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH43" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>85</v>
+        <v>423</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>432</v>
+        <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G44" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G44" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="N44" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>437</v>
-      </c>
       <c r="P44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AG44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH44" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH44" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>85</v>
+        <v>436</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>439</v>
+        <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS44" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>85</v>
+        <v>372</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G46" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G46" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="L46" t="s" s="2">
-        <v>142</v>
-      </c>
       <c r="M46" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AG46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH46" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH46" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>85</v>
+        <v>372</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS46" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G47" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G47" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH47" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH47" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS47" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J48" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="G48" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="K48" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>446</v>
-      </c>
       <c r="O48" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AA48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>85</v>
+        <v>446</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>448</v>
+        <v>217</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>218</v>
@@ -8077,538 +7911,523 @@
         <v>219</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AS48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J49" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="H49" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="K49" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="O49" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="P49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>85</v>
+        <v>451</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>453</v>
+        <v>289</v>
       </c>
       <c r="AP49" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR49" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS49" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>457</v>
-      </c>
       <c r="O50" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="Z50" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AA50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>138</v>
-      </c>
       <c r="AQ50" t="s" s="2">
-        <v>301</v>
+        <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS50" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G51" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G51" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="N51" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>307</v>
-      </c>
       <c r="P51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="Z51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AA51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO51" t="s" s="2">
+      <c r="AP51" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AP51" t="s" s="2">
+      <c r="AQ51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR51" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AR51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS51" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G52" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="G52" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K52" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I52" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="L52" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="P52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AG52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH52" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AH52" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AI52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>85</v>
+        <v>365</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>368</v>
+        <v>84</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS52">
+  <autoFilter ref="A1:AR52">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="463">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -957,6 +957,9 @@
   <si>
     <t>obs-6
 us-core-2</t>
+  </si>
+  <si>
+    <t>null: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -4982,7 +4985,7 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>84</v>
+        <v>299</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>84</v>
@@ -4997,7 +5000,7 @@
         <v>137</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
@@ -5008,14 +5011,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5037,16 +5040,16 @@
         <v>191</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5074,10 +5077,10 @@
         <v>212</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>84</v>
@@ -5095,7 +5098,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5119,27 +5122,27 @@
         <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5162,19 +5165,19 @@
         <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5223,7 +5226,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5250,10 +5253,10 @@
         <v>84</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -5264,10 +5267,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5293,13 +5296,13 @@
         <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5325,13 +5328,13 @@
         <v>84</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>84</v>
@@ -5349,7 +5352,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5373,27 +5376,27 @@
         <v>84</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5419,16 +5422,16 @@
         <v>191</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5453,13 +5456,13 @@
         <v>84</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>84</v>
@@ -5477,7 +5480,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5504,10 +5507,10 @@
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5518,10 +5521,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5544,16 +5547,16 @@
         <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5603,7 +5606,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5627,27 +5630,27 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5670,16 +5673,16 @@
         <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5729,7 +5732,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5753,27 +5756,27 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5796,19 +5799,19 @@
         <v>84</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -5857,7 +5860,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -5869,7 +5872,7 @@
         <v>84</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>84</v>
@@ -5884,10 +5887,10 @@
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -5898,10 +5901,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5924,13 +5927,13 @@
         <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5981,7 +5984,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6011,7 +6014,7 @@
         <v>84</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6022,10 +6025,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6054,7 +6057,7 @@
         <v>141</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>143</v>
@@ -6107,7 +6110,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6137,7 +6140,7 @@
         <v>84</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6148,14 +6151,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6177,10 +6180,10 @@
         <v>140</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>143</v>
@@ -6235,7 +6238,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6276,10 +6279,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6302,13 +6305,13 @@
         <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6359,7 +6362,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6368,7 +6371,7 @@
         <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
@@ -6386,10 +6389,10 @@
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6400,10 +6403,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6426,13 +6429,13 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6483,7 +6486,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6492,7 +6495,7 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
@@ -6510,10 +6513,10 @@
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6524,10 +6527,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6553,16 +6556,16 @@
         <v>191</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6590,10 +6593,10 @@
         <v>118</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6611,7 +6614,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6635,13 +6638,13 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -6652,10 +6655,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6681,16 +6684,16 @@
         <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -6715,13 +6718,13 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -6739,7 +6742,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6763,13 +6766,13 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -6780,10 +6783,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6806,17 +6809,17 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -6865,7 +6868,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -6895,7 +6898,7 @@
         <v>84</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -6906,10 +6909,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6932,13 +6935,13 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6989,7 +6992,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7016,10 +7019,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7030,10 +7033,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7056,16 +7059,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7115,7 +7118,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7142,10 +7145,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7156,10 +7159,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7182,16 +7185,16 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7241,7 +7244,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7268,10 +7271,10 @@
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7282,10 +7285,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7308,19 +7311,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7369,7 +7372,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7396,10 +7399,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7410,10 +7413,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7436,13 +7439,13 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7493,7 +7496,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7523,7 +7526,7 @@
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7534,10 +7537,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7566,7 +7569,7 @@
         <v>141</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>143</v>
@@ -7619,7 +7622,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7649,7 +7652,7 @@
         <v>84</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7660,14 +7663,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7689,10 +7692,10 @@
         <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>143</v>
@@ -7747,7 +7750,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7788,10 +7791,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7817,13 +7820,13 @@
         <v>191</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O48" t="s" s="2">
         <v>211</v>
@@ -7851,10 +7854,10 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Z48" t="s" s="2">
         <v>214</v>
@@ -7875,7 +7878,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>94</v>
@@ -7899,7 +7902,7 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>217</v>
@@ -7916,10 +7919,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7945,13 +7948,13 @@
         <v>281</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O49" t="s" s="2">
         <v>285</v>
@@ -8003,7 +8006,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8027,7 +8030,7 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>289</v>
@@ -8044,10 +8047,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8073,13 +8076,13 @@
         <v>191</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O50" t="s" s="2">
         <v>296</v>
@@ -8110,7 +8113,7 @@
         <v>212</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>297</v>
@@ -8131,7 +8134,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8140,7 +8143,7 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
@@ -8161,7 +8164,7 @@
         <v>137</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8172,14 +8175,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8201,16 +8204,16 @@
         <v>191</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8238,10 +8241,10 @@
         <v>212</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8259,7 +8262,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8283,27 +8286,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8329,16 +8332,16 @@
         <v>85</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8387,7 +8390,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8414,10 +8417,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -959,7 +959,7 @@
 us-core-2</t>
   </si>
   <si>
-    <t>null: target not supported</t>
+    <t>2031: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$52</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2189" uniqueCount="465">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
+    <t>Mapping: Virtual Patient Record (VPR)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -733,6 +736,9 @@
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
+  </si>
+  <si>
+    <t>demographics.lrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1789,7 +1795,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR52"/>
+  <dimension ref="A1:AS52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -1829,12 +1835,13 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1970,6 +1977,9 @@
       <c r="AR1" t="s" s="1">
         <v>80</v>
       </c>
+      <c r="AS1" t="s" s="1">
+        <v>81</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1980,106 +1990,106 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>90</v>
@@ -2091,1135 +2101,1162 @@
         <v>92</v>
       </c>
       <c r="AQ2" t="s" s="2">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="AR2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS2" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AQ3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AR3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS3" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AQ4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AR4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS4" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AQ5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AR5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS5" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AQ6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AR6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS6" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP7" t="s" s="2">
-        <v>129</v>
+        <v>85</v>
       </c>
       <c r="AQ7" t="s" s="2">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="AR7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS7" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH8" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP8" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ8" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS8" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH9" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AG9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP9" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ9" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS9" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH10" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AG10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP10" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ10" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS10" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH11" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>85</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>157</v>
+        <v>85</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>158</v>
@@ -3228,370 +3265,379 @@
         <v>159</v>
       </c>
       <c r="AR11" t="s" s="2">
-        <v>84</v>
+        <v>160</v>
+      </c>
+      <c r="AS11" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH12" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>167</v>
+        <v>85</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>168</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AR12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS12" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH13" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>177</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>84</v>
+        <v>178</v>
       </c>
       <c r="AR13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS13" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>185</v>
+        <v>85</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>186</v>
@@ -3606,376 +3652,385 @@
         <v>189</v>
       </c>
       <c r="AR14" t="s" s="2">
-        <v>84</v>
+        <v>190</v>
+      </c>
+      <c r="AS14" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH15" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AE15" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>202</v>
+        <v>85</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>203</v>
       </c>
       <c r="AR15" t="s" s="2">
-        <v>84</v>
+        <v>204</v>
+      </c>
+      <c r="AS15" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH16" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S16" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>202</v>
+        <v>85</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>203</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>84</v>
+        <v>204</v>
+      </c>
+      <c r="AS16" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>215</v>
+        <v>85</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>216</v>
@@ -3991,3921 +4046,4014 @@
       </c>
       <c r="AR17" t="s" s="2">
         <v>220</v>
+      </c>
+      <c r="AS17" t="s" s="2">
+        <v>221</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AR18" t="s" s="2">
-        <v>84</v>
+        <v>234</v>
+      </c>
+      <c r="AS18" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH19" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>217</v>
+        <v>85</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>84</v>
+        <v>234</v>
+      </c>
+      <c r="AS19" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>246</v>
+        <v>85</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>84</v>
+        <v>248</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>247</v>
+        <v>85</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>84</v>
+        <v>251</v>
+      </c>
+      <c r="AS20" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>259</v>
+        <v>85</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>84</v>
+        <v>261</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>260</v>
+        <v>85</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>84</v>
+        <v>264</v>
+      </c>
+      <c r="AS21" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>268</v>
+        <v>85</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>84</v>
+        <v>272</v>
+      </c>
+      <c r="AS22" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH23" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>276</v>
+        <v>85</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>277</v>
+        <v>85</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>84</v>
+        <v>281</v>
+      </c>
+      <c r="AS23" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>288</v>
+        <v>85</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>291</v>
+        <v>85</v>
+      </c>
+      <c r="AS24" t="s" s="2">
+        <v>293</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>300</v>
+        <v>138</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>84</v>
+        <v>302</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS25" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH26" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>309</v>
+        <v>85</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>84</v>
+        <v>313</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>312</v>
+        <v>85</v>
+      </c>
+      <c r="AS26" t="s" s="2">
+        <v>314</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH27" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>319</v>
+        <v>85</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>84</v>
+        <v>322</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS27" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>328</v>
+        <v>85</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>84</v>
+        <v>332</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>331</v>
+        <v>85</v>
+      </c>
+      <c r="AS28" t="s" s="2">
+        <v>333</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>339</v>
+        <v>85</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>84</v>
+        <v>342</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS29" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>346</v>
+        <v>85</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>84</v>
+        <v>350</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>349</v>
+        <v>85</v>
+      </c>
+      <c r="AS30" t="s" s="2">
+        <v>351</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>355</v>
+        <v>85</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>358</v>
+        <v>85</v>
+      </c>
+      <c r="AS31" t="s" s="2">
+        <v>360</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH32" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>366</v>
+        <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>84</v>
+        <v>369</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS32" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>373</v>
+        <v>85</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS33" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH34" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>373</v>
+        <v>85</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS34" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH35" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS35" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>387</v>
+        <v>85</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>84</v>
+        <v>390</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS36" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AG37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>392</v>
-      </c>
       <c r="AQ37" t="s" s="2">
-        <v>84</v>
+        <v>394</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS37" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AA38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>400</v>
+        <v>85</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>311</v>
+        <v>403</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>84</v>
+        <v>313</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS38" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="P39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH39" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF39" t="s" s="2">
+      <c r="AI39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AG39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>401</v>
-      </c>
       <c r="AP39" t="s" s="2">
-        <v>311</v>
+        <v>403</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>84</v>
+        <v>313</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS39" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="P40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>414</v>
+        <v>85</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>84</v>
+        <v>416</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS40" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>387</v>
+        <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>418</v>
+        <v>389</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS41" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH42" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>424</v>
+        <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>84</v>
+        <v>427</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS42" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH43" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF43" t="s" s="2">
+      <c r="AI43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AG43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>431</v>
-      </c>
       <c r="AQ43" t="s" s="2">
-        <v>84</v>
+        <v>433</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS43" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="P44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH44" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>437</v>
+        <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>84</v>
+        <v>440</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS44" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>373</v>
+        <v>85</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS45" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH46" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>373</v>
+        <v>85</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS46" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH47" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS47" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AA48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>447</v>
+        <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>217</v>
+        <v>449</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>218</v>
@@ -7914,523 +8062,538 @@
         <v>219</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>84</v>
+        <v>220</v>
+      </c>
+      <c r="AS48" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>452</v>
+        <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>289</v>
+        <v>454</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>291</v>
+        <v>85</v>
+      </c>
+      <c r="AS49" t="s" s="2">
+        <v>293</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AA50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>300</v>
+        <v>138</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>84</v>
+        <v>302</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS50" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH51" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>309</v>
+        <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>84</v>
+        <v>313</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>312</v>
+        <v>85</v>
+      </c>
+      <c r="AS51" t="s" s="2">
+        <v>314</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH52" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="S52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AI52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>366</v>
+        <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>84</v>
+        <v>369</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="AS52" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR52">
+  <autoFilter ref="A1:AS52">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -738,7 +738,8 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn</t>
+    <t>demographics.lrdfn
+accession.collected</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -1836,7 +1836,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -738,8 +738,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn
-accession.collected</t>
+    <t>Patient.PatientExtension.VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -738,7 +738,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>Patient.PatientExtension.VeteranLrdfn</t>
+    <t>Patient.Extension[PatientExtension].VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PATIENT (2) to us-core-observation-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file PATIENT (2) to us-core-observation-lab.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -732,7 +732,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
+    <t>844: reference based on PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
@@ -1833,7 +1833,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="92.17578125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -629,6 +629,31 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:Laboratory</t>
+  </si>
+  <si>
+    <t>Laboratory</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -639,32 +664,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>843: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#laboratory</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:Laboratory</t>
-  </si>
-  <si>
-    <t>Laboratory</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -3708,7 +3708,7 @@
         <v>85</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>197</v>
+        <v>85</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>85</v>
@@ -3726,23 +3726,23 @@
         <v>119</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>191</v>
@@ -3760,28 +3760,28 @@
         <v>107</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP15" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ15" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AR15" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AQ15" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AR15" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="AS15" t="s" s="2">
         <v>85</v>
@@ -3789,13 +3789,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>191</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>85</v>
@@ -3839,7 +3839,7 @@
         <v>85</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>85</v>
@@ -3857,10 +3857,10 @@
         <v>119</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>85</v>
@@ -3893,7 +3893,7 @@
         <v>107</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>85</v>
@@ -3911,10 +3911,10 @@
         <v>85</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AS16" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
